--- a/tests/fixtures/comments.xlsx
+++ b/tests/fixtures/comments.xlsx
@@ -18,8 +18,18 @@
         <r>
           <t>昔のメモ</t>
         </r>
+        <rPh sb="0" eb="2">
+          <t>ムカシ</t>
+        </rPh>
         <r>
           <t>の続き</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="9">
+      <text>
+        <r>
+          <t>範囲外のメモ</t>
         </r>
       </text>
     </comment>
